--- a/Images/1/Analytics.xlsx
+++ b/Images/1/Analytics.xlsx
@@ -448,19 +448,19 @@
         <v>6</v>
       </c>
       <c r="C4" s="2">
-        <v>4.523798686893844</v>
+        <v>4.128855869318998</v>
       </c>
       <c r="D4" s="2">
-        <v>0.1309496717234611</v>
+        <v>0.03221396732974946</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>1.333981101463021</v>
+        <v>4.128855869318998</v>
       </c>
       <c r="G4" s="2">
-        <v>0.0004858260972657735</v>
+        <v>0.1238764967107402</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -469,17 +469,17 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="2">
-        <v>4.087667060693431</v>
+        <v>4.188345249652122</v>
       </c>
       <c r="D5" s="2">
-        <v>0.02191676517335783</v>
+        <v>0.04708631241303052</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="2">
-        <v>1.109874412454852</v>
+        <v>4.188345249652122</v>
       </c>
       <c r="G5" s="2">
-        <v>0.1675941906588611</v>
+        <v>0.05664830967725515</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -488,17 +488,17 @@
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="2">
-        <v>3.955712660241945</v>
+        <v>3.943068308947816</v>
       </c>
       <c r="D6" s="2">
-        <v>0.01107183493951369</v>
+        <v>0.01423292276304611</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="2">
-        <v>1.397609689867703</v>
+        <v>3.943068308947816</v>
       </c>
       <c r="G6" s="2">
-        <v>0.04820726740077735</v>
+        <v>0.03504836175016568</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -507,17 +507,17 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="2">
-        <v>3.982546455255272</v>
+        <v>3.91124524629996</v>
       </c>
       <c r="D7" s="2">
-        <v>0.004363386186182039</v>
+        <v>0.02218868842500998</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="2">
-        <v>1.321592651220952</v>
+        <v>3.91124524629996</v>
       </c>
       <c r="G7" s="2">
-        <v>0.008805511584285663</v>
+        <v>0.003522875145473781</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -526,17 +526,17 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="2">
-        <v>3.999707402184866</v>
+        <v>3.999518517387692</v>
       </c>
       <c r="D8" s="2">
-        <v>7.314945378344984E-05</v>
+        <v>0.0001203706530770177</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="2">
-        <v>1.332936531124977</v>
+        <v>3.999518517387692</v>
       </c>
       <c r="G8" s="2">
-        <v>0.000297601656267521</v>
+        <v>0.0005785473592094803</v>
       </c>
     </row>
   </sheetData>

--- a/Images/1/Analytics.xlsx
+++ b/Images/1/Analytics.xlsx
@@ -448,19 +448,19 @@
         <v>6</v>
       </c>
       <c r="C4" s="2">
-        <v>4.128855869318998</v>
+        <v>3.729669485359262</v>
       </c>
       <c r="D4" s="2">
-        <v>0.03221396732974946</v>
+        <v>0.06758262866018461</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>4.128855869318998</v>
+        <v>1.613234778933437</v>
       </c>
       <c r="G4" s="2">
-        <v>0.1238764967107402</v>
+        <v>0.2099260842000779</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -469,17 +469,17 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="2">
-        <v>4.188345249652122</v>
+        <v>4.076002015902302</v>
       </c>
       <c r="D5" s="2">
-        <v>0.04708631241303052</v>
+        <v>0.0190005039755754</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="2">
-        <v>4.188345249652122</v>
+        <v>1.366019625195808</v>
       </c>
       <c r="G5" s="2">
-        <v>0.05664830967725515</v>
+        <v>0.02451471889685597</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -488,17 +488,17 @@
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="2">
-        <v>3.943068308947816</v>
+        <v>3.948933814718318</v>
       </c>
       <c r="D6" s="2">
-        <v>0.01423292276304611</v>
+        <v>0.0127665463204204</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="2">
-        <v>3.943068308947816</v>
+        <v>1.376358145337994</v>
       </c>
       <c r="G6" s="2">
-        <v>0.03504836175016568</v>
+        <v>0.03226860900349593</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -507,17 +507,17 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="2">
-        <v>3.91124524629996</v>
+        <v>3.985637257659442</v>
       </c>
       <c r="D7" s="2">
-        <v>0.02218868842500998</v>
+        <v>0.003590685585139419</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="2">
-        <v>3.91124524629996</v>
+        <v>1.353475042545445</v>
       </c>
       <c r="G7" s="2">
-        <v>0.003522875145473781</v>
+        <v>0.01510628190908392</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -526,17 +526,17 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="2">
-        <v>3.999518517387692</v>
+        <v>4.000051520609456</v>
       </c>
       <c r="D8" s="2">
-        <v>0.0001203706530770177</v>
+        <v>1.288015236400319E-05</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="2">
-        <v>3.999518517387692</v>
+        <v>1.333094306224752</v>
       </c>
       <c r="G8" s="2">
-        <v>0.0005785473592094803</v>
+        <v>0.0001792703314362765</v>
       </c>
     </row>
   </sheetData>

--- a/Images/1/Analytics.xlsx
+++ b/Images/1/Analytics.xlsx
@@ -34,16 +34,19 @@
     <t>Оценка дисперсии Dx</t>
   </si>
   <si>
-    <t>4.000000</t>
-  </si>
-  <si>
-    <t>1.333333</t>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>1.333</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -96,12 +99,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -396,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -447,20 +451,20 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2">
-        <v>3.729669485359262</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.06758262866018461</v>
+      <c r="C4" s="3">
+        <v>3.789600864157442</v>
+      </c>
+      <c r="D4" s="3">
+        <v>5.259978396063946</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="2">
-        <v>1.613234778933437</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.2099260842000779</v>
+      <c r="F4" s="3">
+        <v>1.548346813711923</v>
+      </c>
+      <c r="G4" s="3">
+        <v>16.12601102839423</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -468,18 +472,18 @@
         <v>100</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="2">
-        <v>4.076002015902302</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.0190005039755754</v>
+      <c r="C5" s="3">
+        <v>4.028537975945082</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.7134493986270529</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="2">
-        <v>1.366019625195808</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.02451471889685597</v>
+      <c r="F5" s="3">
+        <v>1.303157865063814</v>
+      </c>
+      <c r="G5" s="3">
+        <v>2.263160120213925</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -487,18 +491,18 @@
         <v>500</v>
       </c>
       <c r="B6" s="1"/>
-      <c r="C6" s="2">
-        <v>3.948933814718318</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.0127665463204204</v>
+      <c r="C6" s="3">
+        <v>4.011422724105626</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.2855681026406431</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="2">
-        <v>1.376358145337994</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.03226860900349593</v>
+      <c r="F6" s="3">
+        <v>1.304003649016951</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2.199726323728646</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -506,37 +510,18 @@
         <v>1000</v>
       </c>
       <c r="B7" s="1"/>
-      <c r="C7" s="2">
-        <v>3.985637257659442</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.003590685585139419</v>
+      <c r="C7" s="3">
+        <v>4.000747641709548</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.01869104273870548</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="2">
-        <v>1.353475042545445</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.01510628190908392</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2">
-        <v>4.000051520609456</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1.288015236400319E-05</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2">
-        <v>1.333094306224752</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.0001792703314362765</v>
+      <c r="F7" s="3">
+        <v>1.344189276232988</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.814195717474131</v>
       </c>
     </row>
   </sheetData>
@@ -548,8 +533,8 @@
     <mergeCell ref="E1:E3"/>
     <mergeCell ref="F1:F3"/>
     <mergeCell ref="G1:G3"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="E4:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
